--- a/data/trans_dic/P40_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P40_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud bueno o muy bueno (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es buena o muy buena (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>73,09%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>79,44; 85,4</t>
+          <t>79,58; 85,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,39; 84,29</t>
+          <t>78,25; 84,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,04; 85,54</t>
+          <t>79,75; 85,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73,26; 79,67</t>
+          <t>73,82; 80,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,46; 75,62</t>
+          <t>68,71; 75,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,05; 75,76</t>
+          <t>68,58; 75,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,39; 74,43</t>
+          <t>67,34; 74,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,16; 71,49</t>
+          <t>66,66; 72,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,89; 79,32</t>
+          <t>74,94; 79,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74,51; 79,05</t>
+          <t>74,55; 79,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74,47; 79,09</t>
+          <t>74,39; 79,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,4; 74,66</t>
+          <t>70,82; 75,1</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>78,13%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,29; 86,71</t>
+          <t>82,03; 86,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,27; 85,85</t>
+          <t>81,22; 86,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,11; 86,59</t>
+          <t>82,12; 86,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,6; 93,97</t>
+          <t>81,67; 86,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,37; 70,44</t>
+          <t>64,39; 70,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,52; 76,37</t>
+          <t>70,63; 76,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,19; 77,98</t>
+          <t>72,56; 78,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>69,88; 74,63</t>
+          <t>69,98; 74,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,17; 78,0</t>
+          <t>74,02; 77,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76,73; 80,42</t>
+          <t>76,55; 80,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,14; 81,84</t>
+          <t>78,07; 81,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,32; 87,19</t>
+          <t>76,5; 79,73</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>78,91%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,03; 87,55</t>
+          <t>81,84; 87,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,05; 87,13</t>
+          <t>81,07; 86,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,58; 86,9</t>
+          <t>81,26; 86,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78,19; 84,51</t>
+          <t>79,39; 85,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>72,02; 78,67</t>
+          <t>72,11; 78,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,74; 76,42</t>
+          <t>69,67; 76,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,66; 80,83</t>
+          <t>74,57; 81,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75,24; 91,1</t>
+          <t>72,75; 78,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77,95; 82,12</t>
+          <t>77,86; 82,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>76,4; 80,79</t>
+          <t>76,48; 80,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79,11; 83,08</t>
+          <t>79,03; 83,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>78,13; 87,27</t>
+          <t>77,07; 80,8</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,63; 86,17</t>
+          <t>81,66; 86,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,89; 85,09</t>
+          <t>79,95; 85,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,71; 86,38</t>
+          <t>81,78; 86,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77,8; 82,78</t>
+          <t>78,33; 83,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,99; 74,89</t>
+          <t>69,43; 74,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,74; 75,51</t>
+          <t>70,21; 75,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,51; 77,4</t>
+          <t>71,4; 77,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,51; 72,72</t>
+          <t>69,79; 74,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76,05; 79,8</t>
+          <t>75,92; 79,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75,58; 79,36</t>
+          <t>75,39; 79,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77,2; 81,05</t>
+          <t>77,18; 80,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64,39; 76,58</t>
+          <t>74,75; 78,02</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,67; 85,29</t>
+          <t>82,78; 85,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>81,61; 84,39</t>
+          <t>81,59; 84,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,69; 85,25</t>
+          <t>82,6; 85,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,16; 85,94</t>
+          <t>79,98; 82,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>69,85; 73,07</t>
+          <t>69,81; 72,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,53; 74,64</t>
+          <t>71,51; 74,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,22; 76,33</t>
+          <t>73,2; 76,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>68,71; 77,11</t>
+          <t>71,19; 73,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>76,63; 78,6</t>
+          <t>76,59; 78,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76,96; 78,95</t>
+          <t>76,91; 79,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78,41; 80,23</t>
+          <t>78,26; 80,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,83; 80,02</t>
+          <t>75,89; 77,65</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud bueno o muy bueno (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es buena o muy buena (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486174</t>
+          <t>531528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>466161</t>
+          <t>508839</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>952335</t>
+          <t>1040366</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>551330; 592714</t>
+          <t>552287; 592605</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>547021; 588186</t>
+          <t>546025; 589631</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>535979; 572780</t>
+          <t>533998; 572962</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>465499; 506283</t>
+          <t>509907; 553356</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>471278; 520558</t>
+          <t>472961; 518794</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>478411; 524899</t>
+          <t>475154; 523413</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>450540; 497598</t>
+          <t>450200; 495778</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>446807; 482811</t>
+          <t>488439; 527873</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1035315; 1096462</t>
+          <t>1035885; 1097063</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1036233; 1099321</t>
+          <t>1036728; 1098985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>996592; 1058390</t>
+          <t>995528; 1058466</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>922769; 978707</t>
+          <t>1008091; 1069003</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1035456</t>
+          <t>879952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>692665</t>
+          <t>776252</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1728122</t>
+          <t>1656205</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>790668; 833151</t>
+          <t>788151; 834086</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>817126; 863125</t>
+          <t>816618; 867309</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>836295; 881935</t>
+          <t>836384; 881756</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>985327; 1120933</t>
+          <t>856621; 902865</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>623347; 682097</t>
+          <t>623569; 683292</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>724896; 784958</t>
+          <t>726035; 783430</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>746553; 806404</t>
+          <t>750287; 810701</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>669553; 715046</t>
+          <t>749352; 800443</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1430791; 1504744</t>
+          <t>1427912; 1501626</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1560092; 1635104</t>
+          <t>1556513; 1633778</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1603994; 1679909</t>
+          <t>1602560; 1679229</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1663168; 1875390</t>
+          <t>1621517; 1690042</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>574346</t>
+          <t>661709</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>760975</t>
+          <t>612966</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1335320</t>
+          <t>1274674</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>555838; 593185</t>
+          <t>554512; 593648</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>603607; 648948</t>
+          <t>603811; 647381</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>618696; 659087</t>
+          <t>616326; 659381</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>550992; 595498</t>
+          <t>637520; 683535</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>491201; 536538</t>
+          <t>491811; 535255</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>538531; 590137</t>
+          <t>538021; 590555</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>580249; 628198</t>
+          <t>579480; 629577</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>702283; 850286</t>
+          <t>590934; 633917</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1059840; 1116504</t>
+          <t>1058600; 1117753</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1158918; 1225553</t>
+          <t>1160134; 1226000</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1214748; 1275818</t>
+          <t>1213499; 1275860</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1279733; 1429602</t>
+          <t>1244950; 1305240</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>744576</t>
+          <t>801046</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>738332</t>
+          <t>808192</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1482908</t>
+          <t>1609239</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>768388; 811162</t>
+          <t>768684; 810370</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>746567; 795126</t>
+          <t>747069; 794641</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>757215; 800445</t>
+          <t>757816; 800756</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>721080; 767228</t>
+          <t>775511; 823913</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>716553; 777826</t>
+          <t>721080; 777479</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>726820; 786896</t>
+          <t>731708; 788703</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>739806; 800688</t>
+          <t>738667; 798245</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>585858; 796274</t>
+          <t>781009; 832743</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1505767; 1580054</t>
+          <t>1503158; 1580002</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1493948; 1568633</t>
+          <t>1490132; 1567054</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1513998; 1589574</t>
+          <t>1513606; 1587793</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1301812; 1548321</t>
+          <t>1576464; 1645544</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2840552</t>
+          <t>2874234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2658133</t>
+          <t>2706250</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5498686</t>
+          <t>5580484</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2706368; 2792019</t>
+          <t>2710132; 2790716</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2760419; 2854379</t>
+          <t>2759784; 2856332</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2789225; 2875766</t>
+          <t>2786301; 2877168</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2773520; 2973323</t>
+          <t>2825560; 2918160</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2359049; 2467710</t>
+          <t>2357868; 2465095</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2528669; 2638493</t>
+          <t>2528033; 2634771</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2573184; 2682369</t>
+          <t>2572527; 2680009</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2515853; 2823690</t>
+          <t>2658907; 2753058</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5096678; 5227843</t>
+          <t>5094118; 5234445</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5323512; 5461653</t>
+          <t>5320468; 5472520</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5400612; 5525809</t>
+          <t>5390043; 5532141</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5329362; 5698928</t>
+          <t>5515307; 5643081</t>
         </is>
       </c>
     </row>
